--- a/题库/PY程序设计模拟题4.xlsx
+++ b/题库/PY程序设计模拟题4.xlsx
@@ -831,116 +831,12 @@
     <t>程序改错：折扣计算程序中的三处错误修改。</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11.5"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>【</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.5"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="Segoe UI"/>
-        <charset val="134"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.5"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>】</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.5"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="Segoe UI"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> if customer price&gt;=50 and customer pricec=100: if customer pricex=100 and customer price&gt;=50:if 100&gt;= customer price&gt;=50:air 50&lt;= customer price&lt;=100: 
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.5"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>【</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.5"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="Segoe UI"/>
-        <charset val="134"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.5"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>】</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.5"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="Segoe UI"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> elif customer price&gt;100: 
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.5"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>【</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.5"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="Segoe UI"/>
-        <charset val="134"/>
-      </rPr>
-      <t>3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.5"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>】</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.5"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="Segoe UI"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> printV"disconunt 20%6, after discount you shoud pay (". format(customer price'(1-0.2) t print("disconunt 20%, after discount you shoud pay {}".format(customer price*0.8))</t>
-    </r>
+    <t>【1】 if customer price&gt;=50 and customer pricec=100:
+    if customer pricex=100 and customer price&gt;=50:
+        if 100&gt;= customer price&gt;=50:
+            air 50&lt;= customer price&lt;=100:
+【2】 elif customer price&gt;100:
+【3】     printV"disconunt 20%6, after discount you shoud pay (". format(customer price'(1-0.2) t print("disconunt 20%, after discount you shoud pay {}".format(customer price*0.8))</t>
   </si>
   <si>
     <t>Prog1.4.3.py</t>
